--- a/downloads/customer-crm.xlsx
+++ b/downloads/customer-crm.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성표" sheetId="1" r:id="Re9a48f179e8b4049"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성표" sheetId="1" r:id="R718920779b444deb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -533,7 +533,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="30" t="str">
-        <x:v>거상 창업내비 · 실무용 자료 · 기관 발급 문서나 법정 서식을 대체하지 않습니다.</x:v>
+        <x:v>거상창업가이드 · 실무용 자료 · 기관 발급 문서나 법정 서식을 대체하지 않습니다.</x:v>
       </x:c>
       <x:c r="B17" s="30"/>
       <x:c r="C17" s="30"/>
